--- a/awbs.xlsx
+++ b/awbs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/glebkuimov/Desktop/suka/tesis/svo_tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B72F4B-C25D-FB44-81EF-E0BDD4467007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55981E98-FC42-E14A-94FF-0269ED007AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="189">
   <si>
     <t>КЦ</t>
   </si>
@@ -451,18 +451,33 @@
     <t>555-08392053</t>
   </si>
   <si>
+    <t>06.03.2025</t>
+  </si>
+  <si>
     <t>555-08392064</t>
   </si>
   <si>
+    <t>04.03.2025</t>
+  </si>
+  <si>
     <t>555-08392075</t>
   </si>
   <si>
+    <t>09.03.2025</t>
+  </si>
+  <si>
     <t>555-08392086</t>
   </si>
   <si>
+    <t>08.03.2025</t>
+  </si>
+  <si>
     <t>555-08392090</t>
   </si>
   <si>
+    <t>07.03.2025</t>
+  </si>
+  <si>
     <t>555-08392101</t>
   </si>
   <si>
@@ -475,18 +490,30 @@
     <t>555-08392134</t>
   </si>
   <si>
+    <t>12.03.2025</t>
+  </si>
+  <si>
     <t>555-08392145</t>
   </si>
   <si>
+    <t>13.03.2025</t>
+  </si>
+  <si>
     <t>555-08392156</t>
   </si>
   <si>
+    <t>10.03.2025</t>
+  </si>
+  <si>
     <t>555-08392160</t>
   </si>
   <si>
     <t>555-08392171</t>
   </si>
   <si>
+    <t>11.03.2025</t>
+  </si>
+  <si>
     <t>555-08392182</t>
   </si>
   <si>
@@ -517,239 +544,71 @@
     <t>555-08392274</t>
   </si>
   <si>
-    <t>555-08392285</t>
-  </si>
-  <si>
-    <t>555-08392296</t>
-  </si>
-  <si>
-    <t>555-08392300</t>
-  </si>
-  <si>
-    <t>555-08392311</t>
-  </si>
-  <si>
-    <t>555-08392322</t>
-  </si>
-  <si>
-    <t>555-08392333</t>
-  </si>
-  <si>
-    <t>555-08392344</t>
-  </si>
-  <si>
-    <t>555-08392355</t>
-  </si>
-  <si>
-    <t>555-08392366</t>
-  </si>
-  <si>
-    <t>555-08392370</t>
-  </si>
-  <si>
-    <t>555-08392381</t>
-  </si>
-  <si>
-    <t>555-08392392</t>
-  </si>
-  <si>
-    <t>555-08392403</t>
-  </si>
-  <si>
-    <t>555-08392414</t>
-  </si>
-  <si>
-    <t>555-08392425</t>
-  </si>
-  <si>
-    <t>555-08392436</t>
-  </si>
-  <si>
-    <t>555-08392440</t>
-  </si>
-  <si>
-    <t>555-08392451</t>
-  </si>
-  <si>
-    <t>555-08392462</t>
-  </si>
-  <si>
-    <t>555-08392473</t>
-  </si>
-  <si>
-    <t>555-08392484</t>
-  </si>
-  <si>
-    <t>555-08392495</t>
-  </si>
-  <si>
-    <t>555-08392506</t>
-  </si>
-  <si>
-    <t>555-08392510</t>
-  </si>
-  <si>
-    <t>555-08392521</t>
-  </si>
-  <si>
-    <t>555-08392532</t>
-  </si>
-  <si>
-    <t>555-08392543</t>
-  </si>
-  <si>
-    <t>555-08392554</t>
-  </si>
-  <si>
-    <t>555-08392565</t>
-  </si>
-  <si>
-    <t>555-08392576</t>
-  </si>
-  <si>
-    <t>555-08392580</t>
-  </si>
-  <si>
-    <t>555-08392591</t>
-  </si>
-  <si>
-    <t>555-08392602</t>
-  </si>
-  <si>
-    <t>555-08392613</t>
-  </si>
-  <si>
-    <t>555-08392624</t>
-  </si>
-  <si>
-    <t>555-08392635</t>
-  </si>
-  <si>
-    <t>555-08392646</t>
-  </si>
-  <si>
-    <t>555-08392650</t>
-  </si>
-  <si>
-    <t>555-08392661</t>
-  </si>
-  <si>
-    <t>555-08392672</t>
-  </si>
-  <si>
-    <t>555-08392683</t>
-  </si>
-  <si>
-    <t>555-08392694</t>
-  </si>
-  <si>
-    <t>555-08392705</t>
-  </si>
-  <si>
-    <t>555-08392716</t>
-  </si>
-  <si>
-    <t>555-08392720</t>
-  </si>
-  <si>
-    <t>555-08392731</t>
-  </si>
-  <si>
-    <t>555-08392742</t>
-  </si>
-  <si>
-    <t>555-08392753</t>
-  </si>
-  <si>
-    <t>555-08392764</t>
-  </si>
-  <si>
-    <t>555-08392775</t>
-  </si>
-  <si>
-    <t>555-08392786</t>
-  </si>
-  <si>
-    <t>555-08392790</t>
-  </si>
-  <si>
-    <t>555-08392801</t>
-  </si>
-  <si>
-    <t>555-08392812</t>
-  </si>
-  <si>
-    <t>555-08392823</t>
-  </si>
-  <si>
-    <t>555-08392834</t>
-  </si>
-  <si>
-    <t>555-08392845</t>
-  </si>
-  <si>
-    <t>555-08392856</t>
-  </si>
-  <si>
-    <t>555-08392860</t>
-  </si>
-  <si>
-    <t>555-08392871</t>
-  </si>
-  <si>
-    <t>555-08392882</t>
-  </si>
-  <si>
-    <t>555-08392893</t>
-  </si>
-  <si>
-    <t>555-08392904</t>
-  </si>
-  <si>
-    <t>555-08392915</t>
-  </si>
-  <si>
-    <t>555-08392926</t>
-  </si>
-  <si>
-    <t>555-08392930</t>
-  </si>
-  <si>
-    <t>555-08392941</t>
-  </si>
-  <si>
-    <t>555-08392952</t>
-  </si>
-  <si>
-    <t>555-08392963</t>
-  </si>
-  <si>
-    <t>555-08392974</t>
-  </si>
-  <si>
-    <t>555-08392985</t>
-  </si>
-  <si>
-    <t>555-08392996</t>
-  </si>
-  <si>
-    <t>555-08393000</t>
-  </si>
-  <si>
-    <t>555-08393011</t>
-  </si>
-  <si>
-    <t>555-08393022</t>
-  </si>
-  <si>
-    <t>555-08393033</t>
+    <t>555-10216614</t>
+  </si>
+  <si>
+    <t>555-10216636</t>
+  </si>
+  <si>
+    <t>555-10216640</t>
+  </si>
+  <si>
+    <t>555-10216651</t>
+  </si>
+  <si>
+    <t>555-10216662</t>
+  </si>
+  <si>
+    <t>555-10216673</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>555-10216625</t>
+  </si>
+  <si>
+    <t>555-10216684</t>
+  </si>
+  <si>
+    <t>555-10216695</t>
+  </si>
+  <si>
+    <t>555-10216706</t>
+  </si>
+  <si>
+    <t>555-10216710</t>
+  </si>
+  <si>
+    <t>555-10216721</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>555-10216754</t>
+  </si>
+  <si>
+    <t>555-10216802</t>
+  </si>
+  <si>
+    <t>555-10216776</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,6 +677,58 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0066CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF3366FF"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF1677FF"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -851,7 +762,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -887,12 +798,87 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -929,8 +915,41 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
@@ -1254,8 +1273,8 @@
     <col min="5" max="5" width="13.6640625" style="14" customWidth="1"/>
     <col min="6" max="9" width="9.1640625" style="14" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" style="14" customWidth="1"/>
-    <col min="11" max="13" width="9.1640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1640625" style="1"/>
+    <col min="11" max="14" width="9.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -2804,7 +2823,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -2815,7 +2834,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -2829,7 +2848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>96</v>
       </c>
@@ -2843,7 +2862,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>96</v>
       </c>
@@ -2857,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>96</v>
       </c>
@@ -2871,7 +2890,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -2885,7 +2904,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -2899,7 +2918,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -2913,16 +2932,29 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B105" s="7" t="s">
+    <row r="105" spans="1:10" s="30" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" s="29" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E105" s="31">
+        <v>429</v>
+      </c>
+      <c r="F105" s="31">
+        <v>1.53</v>
+      </c>
+      <c r="G105" s="31"/>
+      <c r="H105" s="31"/>
+      <c r="I105" s="31"/>
+      <c r="J105" s="31"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>96</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="28" t="s">
         <v>134</v>
       </c>
       <c r="E106">
@@ -2932,21 +2964,25 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+    <row r="107" spans="1:10" s="24" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="22">
         <v>314</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="22">
         <v>1.8839999999999999</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G107" s="25"/>
+      <c r="H107" s="25"/>
+      <c r="I107" s="25"/>
+      <c r="J107" s="25"/>
+    </row>
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>114</v>
       </c>
@@ -2960,7 +2996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -2974,506 +3010,552 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B110" s="21" t="s">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
         <v>138</v>
       </c>
-      <c r="H110" s="14">
-        <f>SUM(E29:E107)</f>
-        <v>31655</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B110" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E110">
+        <v>6</v>
+      </c>
+      <c r="F110">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>140</v>
+      </c>
       <c r="B111" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="H111" s="14">
-        <f>H110-E56-E50-E46-E41-E38-E36-E28</f>
-        <v>30838.5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="E111">
+        <v>269</v>
+      </c>
+      <c r="F111">
+        <v>0.31900000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>142</v>
+      </c>
       <c r="B112" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="E112">
+        <v>150</v>
+      </c>
+      <c r="F112">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>144</v>
+      </c>
       <c r="B113" s="21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+      <c r="E113">
+        <v>305</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>146</v>
+      </c>
       <c r="B114" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E114">
+        <v>189</v>
+      </c>
+      <c r="F114">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>146</v>
+      </c>
+      <c r="B115" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E115">
+        <v>263</v>
+      </c>
+      <c r="F115">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B116" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>138</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="E117">
+        <v>319</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>151</v>
+      </c>
+      <c r="B118" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E118">
+        <v>1368</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>153</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E119">
+        <v>216</v>
+      </c>
+      <c r="F119">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>155</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E120">
+        <v>1848</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>155</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E121">
+        <v>1342</v>
+      </c>
+      <c r="F121">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>158</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="E122">
+        <v>74</v>
+      </c>
+      <c r="F122">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>158</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E123">
+        <v>861</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>144</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="E124">
+        <v>11</v>
+      </c>
+      <c r="F124">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B125" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B115" s="21" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B116" s="21" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B117" s="21" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B118" s="21" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B119" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B120" s="21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B121" s="21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B122" s="21" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B123" s="21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B124" s="21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B125" s="21" t="s">
+      <c r="B126" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="E126">
+        <v>32</v>
+      </c>
+      <c r="F126">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B127" s="21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B126" s="21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B127" s="21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B128" s="21" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B129" s="21" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B130" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B131" s="21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B132" s="21" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B133" s="21" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B134" s="21" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B135" s="21" t="s">
+      <c r="B128" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E128">
+        <v>46</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="E129">
+        <v>581</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B130" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B131" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H131" s="14">
+        <f>E129+E126+E110</f>
+        <v>619</v>
+      </c>
+      <c r="I131" s="14">
+        <f>C130+C131+C132+C137</f>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B132" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B133" s="34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="B134" s="35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="B135" s="35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B136" s="34" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B137" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B138" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B139" s="34" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B136" s="21" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B137" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B138" s="21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B139" s="21" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B140" s="21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B141" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B142" s="21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B143" s="21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B144" s="21" t="s">
-        <v>172</v>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B140" s="39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B141" s="38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B142" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="B143" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="B144" s="41" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B145" s="21" t="s">
-        <v>173</v>
+      <c r="B145" s="27" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B146" s="21" t="s">
-        <v>174</v>
+      <c r="B146" s="26" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B147" s="21" t="s">
-        <v>175</v>
-      </c>
+      <c r="B147" s="37"/>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B148" s="21" t="s">
-        <v>176</v>
-      </c>
+      <c r="B148" s="37"/>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B149" s="21" t="s">
-        <v>177</v>
-      </c>
+      <c r="B149" s="37"/>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B150" s="21" t="s">
-        <v>178</v>
-      </c>
+      <c r="B150" s="37"/>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B151" s="21" t="s">
-        <v>179</v>
-      </c>
+      <c r="B151" s="37"/>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B152" s="21" t="s">
-        <v>180</v>
-      </c>
+      <c r="B152" s="37"/>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B153" s="21" t="s">
-        <v>181</v>
-      </c>
+      <c r="B153" s="37"/>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B154" s="21" t="s">
-        <v>182</v>
-      </c>
+      <c r="B154" s="37"/>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B155" s="21" t="s">
-        <v>183</v>
-      </c>
+      <c r="B155" s="37"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B156" s="21" t="s">
-        <v>184</v>
-      </c>
+      <c r="B156" s="37"/>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B157" s="21" t="s">
-        <v>185</v>
-      </c>
+      <c r="B157" s="37"/>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B158" s="21" t="s">
-        <v>186</v>
-      </c>
+      <c r="B158" s="37"/>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B159" s="21" t="s">
-        <v>187</v>
-      </c>
+      <c r="B159" s="37"/>
     </row>
     <row r="160" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B160" s="21" t="s">
-        <v>188</v>
-      </c>
+      <c r="B160" s="21"/>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B161" s="21" t="s">
-        <v>189</v>
-      </c>
+      <c r="B161" s="21"/>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B162" s="21" t="s">
-        <v>190</v>
-      </c>
+      <c r="B162" s="21"/>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B163" s="21" t="s">
-        <v>191</v>
-      </c>
+      <c r="B163" s="21"/>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B164" s="21" t="s">
-        <v>192</v>
-      </c>
+      <c r="B164" s="21"/>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B165" s="21" t="s">
-        <v>193</v>
-      </c>
+      <c r="B165" s="21"/>
     </row>
     <row r="166" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B166" s="21" t="s">
-        <v>194</v>
-      </c>
+      <c r="B166" s="21"/>
     </row>
     <row r="167" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B167" s="21" t="s">
-        <v>195</v>
-      </c>
+      <c r="B167" s="21"/>
     </row>
     <row r="168" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B168" s="21" t="s">
-        <v>196</v>
-      </c>
+      <c r="B168" s="21"/>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B169" s="21" t="s">
-        <v>197</v>
-      </c>
+      <c r="B169" s="21"/>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B170" s="21" t="s">
-        <v>198</v>
-      </c>
+      <c r="B170" s="21"/>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B171" s="21" t="s">
-        <v>199</v>
-      </c>
+      <c r="B171" s="21"/>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B172" s="21" t="s">
-        <v>200</v>
-      </c>
+      <c r="B172" s="21"/>
     </row>
     <row r="173" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B173" s="21" t="s">
-        <v>201</v>
-      </c>
+      <c r="B173" s="21"/>
     </row>
     <row r="174" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B174" s="21" t="s">
-        <v>202</v>
-      </c>
+      <c r="B174" s="21"/>
     </row>
     <row r="175" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B175" s="21" t="s">
-        <v>203</v>
-      </c>
+      <c r="B175" s="21"/>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B176" s="21" t="s">
-        <v>204</v>
-      </c>
+      <c r="B176" s="21"/>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B177" s="21" t="s">
-        <v>205</v>
-      </c>
+      <c r="B177" s="21"/>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B178" s="21" t="s">
-        <v>206</v>
-      </c>
+      <c r="B178" s="21"/>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B179" s="21" t="s">
-        <v>207</v>
-      </c>
+      <c r="B179" s="21"/>
     </row>
     <row r="180" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B180" s="21" t="s">
-        <v>208</v>
-      </c>
+      <c r="B180" s="21"/>
     </row>
     <row r="181" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B181" s="21" t="s">
-        <v>209</v>
-      </c>
+      <c r="B181" s="21"/>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B182" s="21" t="s">
-        <v>210</v>
-      </c>
+      <c r="B182" s="21"/>
     </row>
     <row r="183" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B183" s="21" t="s">
-        <v>211</v>
-      </c>
+      <c r="B183" s="21"/>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B184" s="21" t="s">
-        <v>212</v>
-      </c>
+      <c r="B184" s="21"/>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B185" s="21" t="s">
-        <v>213</v>
-      </c>
+      <c r="B185" s="21"/>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B186" s="21" t="s">
-        <v>214</v>
-      </c>
+      <c r="B186" s="21"/>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B187" s="21" t="s">
-        <v>215</v>
-      </c>
+      <c r="B187" s="21"/>
     </row>
     <row r="188" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B188" s="21" t="s">
-        <v>216</v>
-      </c>
+      <c r="B188" s="21"/>
     </row>
     <row r="189" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B189" s="21" t="s">
-        <v>217</v>
-      </c>
+      <c r="B189" s="21"/>
     </row>
     <row r="190" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B190" s="21" t="s">
-        <v>218</v>
-      </c>
+      <c r="B190" s="21"/>
     </row>
     <row r="191" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B191" s="21" t="s">
-        <v>219</v>
-      </c>
+      <c r="B191" s="21"/>
     </row>
     <row r="192" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B192" s="21" t="s">
-        <v>220</v>
-      </c>
+      <c r="B192" s="21"/>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B193" s="21" t="s">
-        <v>221</v>
-      </c>
+      <c r="B193" s="21"/>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B194" s="21" t="s">
-        <v>222</v>
-      </c>
+      <c r="B194" s="21"/>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B195" s="21" t="s">
-        <v>223</v>
-      </c>
+      <c r="B195" s="21"/>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B196" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="B196" s="21"/>
     </row>
     <row r="197" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B197" s="21" t="s">
-        <v>225</v>
-      </c>
+      <c r="B197" s="21"/>
     </row>
     <row r="198" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B198" s="21" t="s">
-        <v>226</v>
-      </c>
+      <c r="B198" s="21"/>
     </row>
     <row r="199" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B199" s="21" t="s">
-        <v>227</v>
-      </c>
+      <c r="B199" s="21"/>
     </row>
     <row r="200" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B200" s="21" t="s">
-        <v>228</v>
-      </c>
+      <c r="B200" s="21"/>
     </row>
     <row r="201" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B201" s="21" t="s">
-        <v>229</v>
-      </c>
+      <c r="B201" s="21"/>
     </row>
     <row r="202" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B202" s="21" t="s">
-        <v>230</v>
-      </c>
+      <c r="B202" s="21"/>
     </row>
     <row r="203" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B203" s="21" t="s">
-        <v>231</v>
-      </c>
+      <c r="B203" s="21"/>
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B204" s="21" t="s">
-        <v>232</v>
-      </c>
+      <c r="B204" s="21"/>
     </row>
     <row r="205" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B205" s="21" t="s">
-        <v>233</v>
-      </c>
+      <c r="B205" s="21"/>
     </row>
     <row r="206" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B206" s="21" t="s">
-        <v>234</v>
-      </c>
+      <c r="B206" s="21"/>
     </row>
     <row r="207" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B207" s="21" t="s">
-        <v>235</v>
-      </c>
+      <c r="B207" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:F207" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A7:F207" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters blank="1">
         <filter val="07.02.2025 "/>
@@ -3497,6 +3579,11 @@
       </filters>
     </filterColumn>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="B140" r:id="rId1" display="https://afl.booking-cargo.ru/booking/30464" xr:uid="{1C6465E1-07AD-5748-8799-F8AD238207D5}"/>
+    <hyperlink ref="B141" r:id="rId2" display="https://afl.booking-cargo.ru/booking/31367" xr:uid="{33045476-A0D6-F944-97B2-E4C19F3D0233}"/>
+    <hyperlink ref="B142" r:id="rId3" display="https://afl.booking-cargo.ru/booking/32407" xr:uid="{414D6437-1585-4B46-B69B-E7A0F373F1AF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
